--- a/artfynd/S 1383-2026 artfynd.xlsx
+++ b/artfynd/S 1383-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY205"/>
+  <dimension ref="A1:AZ205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117991518</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012356</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462962</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1104,6 +1124,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118496290</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1213,6 +1238,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610755</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1329,6 +1359,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118005992</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1430,6 +1465,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012210</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1539,6 +1579,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568473</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1648,6 +1693,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568493</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1762,6 +1812,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117991173</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1886,6 +1941,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/15951787</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2012,6 +2072,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/77200010</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2117,6 +2182,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012197</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2222,6 +2292,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012310</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2327,6 +2402,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012327</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2432,6 +2512,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012333</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2537,6 +2622,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012341</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2642,6 +2732,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012347</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2747,6 +2842,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012371</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2852,6 +2952,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012384</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2957,6 +3062,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012435</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3062,6 +3172,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012488</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3167,6 +3282,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012495</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3272,6 +3392,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012500</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3377,6 +3502,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012512</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3482,6 +3612,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012515</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3587,6 +3722,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012520</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3692,6 +3832,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012524</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3797,6 +3942,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012532</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3902,6 +4052,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118495862</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4012,6 +4167,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551916</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4115,6 +4275,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012224</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4222,6 +4387,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012418</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4329,6 +4499,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118496187</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4455,6 +4630,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117987719</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4562,6 +4742,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610777</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4668,6 +4853,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551318</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4770,6 +4960,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117991939</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4884,6 +5079,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118496239</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4998,6 +5198,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118496262</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5100,6 +5305,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117991967</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5202,6 +5412,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117991994</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5304,6 +5519,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117992010</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5406,6 +5626,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117992031</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5508,6 +5733,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117992041</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5610,6 +5840,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117992046</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5712,6 +5947,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117992067</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5818,6 +6058,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012283</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5933,6 +6178,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012475</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6043,6 +6293,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118012486</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6153,6 +6408,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462943</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6263,6 +6523,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462952</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6373,6 +6638,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462967</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6483,6 +6753,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462970</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6593,6 +6868,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462977</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6703,6 +6983,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462984</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6813,6 +7098,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118462990</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6923,6 +7213,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118463069</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7033,6 +7328,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118463108</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7143,6 +7443,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118463115</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7253,6 +7558,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118463125</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7363,6 +7673,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118463134</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7473,6 +7788,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118463141</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7583,6 +7903,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118463152</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7693,6 +8018,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118463183</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7803,6 +8133,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118463218</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7913,6 +8248,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118495855</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8023,6 +8363,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118496200</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8133,6 +8478,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118496212</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8243,6 +8593,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118496218</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8353,6 +8708,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551283</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8463,6 +8823,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551290</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8572,6 +8937,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551307</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8681,6 +9051,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551333</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8790,6 +9165,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551345</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8899,6 +9279,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551356</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9008,6 +9393,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551365</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9117,6 +9507,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551379</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9226,6 +9621,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551382</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9335,6 +9735,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551386</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9444,6 +9849,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551393</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9553,6 +9963,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551425</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9662,6 +10077,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551432</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9771,6 +10191,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551435</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9880,6 +10305,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551438</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9989,6 +10419,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551441</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10098,6 +10533,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551447</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10207,6 +10647,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551450</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10316,6 +10761,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551455</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10425,6 +10875,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551466</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10534,6 +10989,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551476</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10643,6 +11103,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551482</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10752,6 +11217,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551489</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10861,6 +11331,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551493</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10970,6 +11445,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551499</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -11079,6 +11559,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551515</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -11188,6 +11673,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551523</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11297,6 +11787,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551531</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11406,6 +11901,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551541</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11515,6 +12015,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551545</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11624,6 +12129,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551762</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11733,6 +12243,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551772</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11842,6 +12357,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551778</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11951,6 +12471,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551787</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -12060,6 +12585,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551794</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -12169,6 +12699,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551808</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12278,6 +12813,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551811</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12387,6 +12927,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551813</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12496,6 +13041,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551819</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12606,6 +13156,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551822</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12716,6 +13271,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551829</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12826,6 +13386,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551840</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12936,6 +13501,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551859</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -13046,6 +13616,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551869</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -13156,6 +13731,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551875</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13266,6 +13846,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551884</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13376,6 +13961,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551887</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13486,6 +14076,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551889</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13596,6 +14191,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551892</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13706,6 +14306,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551897</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13816,6 +14421,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551900</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13926,6 +14536,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551907</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -14036,6 +14651,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551921</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -14146,6 +14766,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551926</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -14256,6 +14881,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551933</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14366,6 +14996,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551942</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14476,6 +15111,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551948</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14586,6 +15226,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551953</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14696,6 +15341,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551962</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14806,6 +15456,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551967</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14916,6 +15571,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551971</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -15026,6 +15686,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551977</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -15136,6 +15801,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118551980</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -15245,6 +15915,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552001</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -15354,6 +16029,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552006</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15463,6 +16143,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552088</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15572,6 +16257,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552091</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15681,6 +16371,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552094</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15790,6 +16485,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552095</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15899,6 +16599,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552100</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -16008,6 +16713,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552105</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -16117,6 +16827,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552106</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -16226,6 +16941,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552109</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -16335,6 +17055,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552112</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -16444,6 +17169,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552116</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -16553,6 +17283,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552128</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16662,6 +17397,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552162</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16771,6 +17511,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552177</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16880,6 +17625,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552188</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16989,6 +17739,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552198</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -17098,6 +17853,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552201</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -17207,6 +17967,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552203</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -17316,6 +18081,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552205</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -17425,6 +18195,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552207</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -17534,6 +18309,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552209</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -17643,6 +18423,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552213</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17752,6 +18537,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552218</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17861,6 +18651,11 @@
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552220</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17970,6 +18765,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552221</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -18079,6 +18879,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552232</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -18188,6 +18993,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552241</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -18297,6 +19107,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552243</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -18406,6 +19221,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552246</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -18515,6 +19335,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552249</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -18624,6 +19449,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552250</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18733,6 +19563,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552252</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18842,6 +19677,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552256</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18951,6 +19791,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552259</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -19061,6 +19906,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552260</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -19171,6 +20021,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552265</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -19281,6 +20136,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552291</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -19391,6 +20251,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552301</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -19501,6 +20366,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552304</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -19611,6 +20481,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552307</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -19721,6 +20596,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552308</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19831,6 +20711,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552309</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19941,6 +20826,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552312</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -20051,6 +20941,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552315</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -20161,6 +21056,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552320</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -20271,6 +21171,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552328</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -20381,6 +21286,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552352</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -20491,6 +21401,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118552356</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -20601,6 +21516,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568441</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -20711,6 +21631,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568558</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -20821,6 +21746,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568561</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20931,6 +21861,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568575</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -21041,6 +21976,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568581</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -21151,6 +22091,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568589</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -21261,6 +22206,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568610</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -21371,6 +22321,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568615</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -21481,6 +22436,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568624</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -21591,6 +22551,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568655</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -21701,6 +22666,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568657</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -21811,6 +22781,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568667</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -21921,6 +22896,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568687</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -22031,6 +23011,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568690</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -22141,6 +23126,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118568696</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -22251,6 +23241,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610721</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -22361,6 +23356,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610726</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -22471,6 +23471,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610732</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -22581,6 +23586,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610739</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -22691,6 +23701,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610746</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -22801,6 +23816,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118610767</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -22915,8 +23935,219 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118496176</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>